--- a/HUERFANAS INTEGRALY.xlsx
+++ b/HUERFANAS INTEGRALY.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlando\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ORLANDO\Documents\ANTIGRAVITY\MERCADOLIBRE 18042026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50E51819-E534-4A9F-8818-71AC63C52F8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E67F022-3AF7-45B3-8B0C-776380F91E45}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E0DC12A6-8044-45E9-ACBE-8AA25E983EBA}"/>
   </bookViews>
@@ -506,11 +506,6 @@
 HAGA TODAS SUS PREGUNTAS ANTES DE OFERTAR</t>
   </si>
   <si>
-    <t>GATO O AMORTIGUADOR ELEVADOR CAPOT NISSAN ARMADA 2004-2015 Y NISSAN TITAN 2005-2015
-PRECIO POR UNIDAD 
-HAGA TODAS SUS PREGUNTAS ANTES DE OFERTAR</t>
-  </si>
-  <si>
     <t>GATO O AMORTIGUADOR ELEVADOR COMPUERTA FIAT PALIO WEEKEND 2007-2008
 APLICA SOLO RANCHERA 
 PRECIO POR UNIDAD 
@@ -1371,6 +1366,11 @@
   </si>
   <si>
     <t>El producto es un kit o un pack</t>
+  </si>
+  <si>
+    <t>GATO O AMORTIGUADOR ELEVADOR CAPOT NISSAN ARMADA 2004-2015 Y NISSAN TITAN 2005-2015
+PRECIO POR UNIDAD 
+HAGA TODAS SUS PREGUNTAS ANTES DE OFERTAR</t>
   </si>
 </sst>
 </file>
@@ -1624,261 +1624,6 @@
   </cellStyles>
   <dxfs count="70">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFF6969"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFF6969"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFF6969"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFCCFFCC"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFCCFFCC"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Lucida Sans Typewriter"/>
-        <family val="3"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9194"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9194"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;Bs.S&quot;* #,##0.00_-;\-&quot;Bs.S&quot;* #,##0.00_-;_-&quot;Bs.S&quot;* &quot; - &quot;??_-;_-@_-"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FFD3D3D3"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF808080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFAFAD2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF4500"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;Bs.S&quot;* #,##0.00_-;\-&quot;Bs.S&quot;* #,##0.00_-;_-&quot;Bs.S&quot;* &quot; - &quot;??_-;_-@_-"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1960,6 +1705,28 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2022,6 +1789,35 @@
       </border>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF6969"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF6969"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFF6969"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2061,6 +1857,64 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;Bs.S&quot;* #,##0.00_-;\-&quot;Bs.S&quot;* #,##0.00_-;_-&quot;Bs.S&quot;* &quot; - &quot;??_-;_-@_-"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2080,6 +1934,152 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;Bs.S&quot;* #,##0.00_-;\-&quot;Bs.S&quot;* #,##0.00_-;_-&quot;Bs.S&quot;* &quot; - &quot;??_-;_-@_-"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FFD3D3D3"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Lucida Sans Typewriter"/>
+        <family val="3"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9194"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9194"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF808080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFAFAD2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF4500"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3800,75 +3800,75 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{38187445-5642-4C11-A2A3-9037BE623DCA}" name="TablaPublicaciones" displayName="TablaPublicaciones" ref="A1:BL35" totalsRowShown="0" headerRowDxfId="29" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{38187445-5642-4C11-A2A3-9037BE623DCA}" name="TablaPublicaciones" displayName="TablaPublicaciones" ref="A1:BL35" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
   <autoFilter ref="A1:BL35" xr:uid="{38187445-5642-4C11-A2A3-9037BE623DCA}"/>
   <tableColumns count="64">
-    <tableColumn id="1" xr3:uid="{07E8B1C9-37F8-4516-8331-5DBE056FA510}" name="Id" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{557C55CF-46B1-4281-98D3-FDA85EFCFE20}" name="Vendedor" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{07A2162F-C9CE-49C5-BE73-699F8D7F354A}" name="Tienda Oficial" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{07D79BE4-D461-4119-AF88-D8DC8AE9ABE1}" name="Categoría" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{374339AB-C6F7-4C7E-A5A6-CD72E9250054}" name="Tendencias" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{278D5998-4B3C-4BA4-9A7C-A1E120440B11}" name="Título" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{0234EDF1-B990-4044-B1E0-282355656C77}" name="Largo" dataDxfId="22">
+    <tableColumn id="1" xr3:uid="{07E8B1C9-37F8-4516-8331-5DBE056FA510}" name="Id" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{557C55CF-46B1-4281-98D3-FDA85EFCFE20}" name="Vendedor" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{07A2162F-C9CE-49C5-BE73-699F8D7F354A}" name="Tienda Oficial" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{07D79BE4-D461-4119-AF88-D8DC8AE9ABE1}" name="Categoría" dataDxfId="60"/>
+    <tableColumn id="5" xr3:uid="{374339AB-C6F7-4C7E-A5A6-CD72E9250054}" name="Tendencias" dataDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{278D5998-4B3C-4BA4-9A7C-A1E120440B11}" name="Título" dataDxfId="58"/>
+    <tableColumn id="7" xr3:uid="{0234EDF1-B990-4044-B1E0-282355656C77}" name="Largo" dataDxfId="57">
       <calculatedColumnFormula>LEN(TablaPublicaciones[[#This Row],[Título]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E0B87E46-8A56-47D2-BAE9-4BCB2D23A35F}" name="Descripción" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{F4376C87-095C-4FB9-BEFB-D97C5942E3DD}" name="Precio" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{2851AC63-AA68-40EF-AC01-B1CB63CB3F54}" name="Moneda" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{9A486920-D334-49F4-9651-3544B340B8F7}" name="SKU" dataDxfId="67"/>
-    <tableColumn id="12" xr3:uid="{504E12D6-4FFA-4E63-988B-D8351618F850}" name="Estado" dataDxfId="66"/>
-    <tableColumn id="13" xr3:uid="{8C530989-E33E-4C51-BB2A-A69301EA5973}" name="Stock" dataDxfId="65"/>
-    <tableColumn id="14" xr3:uid="{B8F4AAD6-AFC8-453A-BEA4-C8315EA4E074}" name="Tipo de Publicación" dataDxfId="64"/>
-    <tableColumn id="15" xr3:uid="{D515DD2D-9950-499C-A3C9-02EAB564CDB6}" name="Condición" dataDxfId="63"/>
-    <tableColumn id="16" xr3:uid="{D304FA7B-1DB5-467C-B4C0-159C7B76ED81}" name="Envio Gratis" dataDxfId="21"/>
-    <tableColumn id="17" xr3:uid="{4FABBCF4-6194-4782-B178-8C992F5A9BF7}" name="Precio Envio Gratis" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{98934760-3BF6-4D2B-BEE7-A1649AD0AE03}" name="Modo Envio" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{09015D66-D40E-48FC-AA0D-DF7C960CED1C}" name="Metodo Envio" dataDxfId="62"/>
-    <tableColumn id="20" xr3:uid="{74BB07AA-3E72-4250-A57F-C6B07358395F}" name="Retira en Persona" dataDxfId="61"/>
-    <tableColumn id="21" xr3:uid="{9AF8BAC3-B650-4C3D-AF7D-94AD638CD8D1}" name="Envio FLEX" dataDxfId="60"/>
-    <tableColumn id="22" xr3:uid="{D6EDAE76-DF30-4549-8156-D06F228C6AE8}" name="Garantia" dataDxfId="18"/>
-    <tableColumn id="23" xr3:uid="{CA3CB06E-FF35-4B00-8F1F-BE67BBA7A61A}" name="Fecha Creación" dataDxfId="17"/>
-    <tableColumn id="24" xr3:uid="{B9179D59-0B0B-47E5-84C3-450FA1E054DF}" name="Última Actualización" dataDxfId="12"/>
-    <tableColumn id="25" xr3:uid="{35DCB46A-158D-403D-818B-8CBB83F35F5A}" name="Resultado" dataDxfId="11"/>
-    <tableColumn id="26" xr3:uid="{51193C13-B5C6-4AB0-AD61-2582ADED050F}" name="Resultado Observaciones" dataDxfId="9"/>
-    <tableColumn id="27" xr3:uid="{592AE190-9BCD-4633-A51D-AB6AA482AB93}" name="Imagen 1" dataDxfId="10"/>
-    <tableColumn id="28" xr3:uid="{5BCBA99F-8D2E-4EC0-9BC4-CEC88F1CDA88}" name="Imagen 2" dataDxfId="59"/>
-    <tableColumn id="29" xr3:uid="{1DA8AC64-0DDB-4549-828F-B7AAA646A393}" name="Imagen 3" dataDxfId="58"/>
-    <tableColumn id="30" xr3:uid="{E3E11581-3A67-491F-B299-4FA96F0CA2BB}" name="Imagen 4" dataDxfId="57"/>
-    <tableColumn id="31" xr3:uid="{3E72739F-F6D5-413E-A939-3776645507BD}" name="Imagen 5" dataDxfId="56"/>
-    <tableColumn id="32" xr3:uid="{A85C7D82-6155-4554-9B3D-18ED31E78966}" name="Imagen 6" dataDxfId="55"/>
-    <tableColumn id="33" xr3:uid="{DE5CDDDB-F9AD-43F1-9476-B132B7023807}" name="Imagen 7" dataDxfId="54"/>
-    <tableColumn id="34" xr3:uid="{68CE6975-FAB8-4236-8F39-1AA4B658E504}" name="Imagen 8" dataDxfId="53"/>
-    <tableColumn id="35" xr3:uid="{176F89D3-55C1-4864-A9EE-83C429B15147}" name="Imagen 9" dataDxfId="52"/>
-    <tableColumn id="36" xr3:uid="{822D9C27-446E-4C51-834D-EFA6235C1FD1}" name="Imagen 10" dataDxfId="51"/>
-    <tableColumn id="37" xr3:uid="{06003688-CF66-40B9-80A3-0E817EF58334}" name="Visitas" dataDxfId="50"/>
-    <tableColumn id="38" xr3:uid="{867443DD-E155-463F-8AB6-127CAC8F04D7}" name="Vendidos" dataDxfId="16"/>
-    <tableColumn id="39" xr3:uid="{450CCE7E-504E-43B5-996D-68A045978B20}" name="Fecha Ultima Venta" dataDxfId="15"/>
-    <tableColumn id="40" xr3:uid="{F045B770-A77E-4B81-B2C3-B8805902967A}" name="Variación_x000d__x000a_Color" dataDxfId="2"/>
-    <tableColumn id="41" xr3:uid="{1B5F14A3-3B98-4C46-A40D-D6B6D3A92694}" name="Variación_x000d__x000a_Código universal de producto" dataDxfId="0"/>
-    <tableColumn id="42" xr3:uid="{46FC1A21-3FAC-4529-89E5-671FB1C585CF}" name="Variación_x000d__x000a_Código OEM" dataDxfId="1"/>
-    <tableColumn id="43" xr3:uid="{B0BD1BC7-A155-4C36-9BFA-6134205BF2C2}" name="Atributo_x000d__x000a_Marca" dataDxfId="49"/>
-    <tableColumn id="44" xr3:uid="{7DFE1A7F-BFBA-4B08-A268-9FA639E80D6D}" name="Atributo_x000d__x000a_Número de pieza" dataDxfId="48"/>
-    <tableColumn id="45" xr3:uid="{C81DC53D-A59A-4BE3-85CB-7E330249E5A3}" name="Atributo_x000d__x000a_Modelo" dataDxfId="47"/>
-    <tableColumn id="46" xr3:uid="{17D22998-DBB8-4832-B2F1-0651FF94B680}" name="Atributo_x000d__x000a_Formato de venta" dataDxfId="46"/>
-    <tableColumn id="47" xr3:uid="{D119AEAD-E9A2-4AC9-BB22-A998D88D0BA7}" name="Atributo_x000d__x000a_Unidades por pack" dataDxfId="45"/>
-    <tableColumn id="48" xr3:uid="{16708B52-94B7-4A28-8034-BF5B173D0A22}" name="Atributo_x000d__x000a_Largo extendido" dataDxfId="44"/>
-    <tableColumn id="49" xr3:uid="{67FDACCE-02CC-47CE-BC26-2CCAD33D28DF}" name="Atributo_x000d__x000a_Largo comprimido" dataDxfId="43"/>
-    <tableColumn id="50" xr3:uid="{4C316B6B-2322-4B67-9371-CEFB9BF5BC1E}" name="Atributo_x000d__x000a_Lugar de colocación" dataDxfId="42"/>
-    <tableColumn id="51" xr3:uid="{B7C39FD4-4950-4A18-B31E-65EA4E00CCB0}" name="Atributo_x000d__x000a_Origen" dataDxfId="41"/>
-    <tableColumn id="52" xr3:uid="{4750DCC5-91A5-4023-8D76-2FABC2DB19D1}" name="Atributo_x000d__x000a_Tipo de vehículo" dataDxfId="5"/>
-    <tableColumn id="53" xr3:uid="{311F8834-A35A-421E-9403-BC70515A42D0}" name="Atributo_x000d__x000a_Código universal de producto" dataDxfId="3"/>
-    <tableColumn id="54" xr3:uid="{A6B39D83-4E6C-473C-AF8F-03D5F386FB74}" name="Atributo_x000d__x000a_Código OEM" dataDxfId="4"/>
-    <tableColumn id="55" xr3:uid="{D281CDC7-FACC-4E01-AB6B-7D3FBC5D4615}" name="Atributo_x000d__x000a_Motivo de GTIN vacío" dataDxfId="40"/>
-    <tableColumn id="56" xr3:uid="{3345F854-C43F-427B-BADA-ACF763FA14DB}" name="Atributo_x000d__x000a_Material del núcleo" dataDxfId="39"/>
-    <tableColumn id="57" xr3:uid="{D181DC2A-403B-4CA6-9E8A-872ED1FD375B}" name="Atributo_x000d__x000a_Cantidad de llaves" dataDxfId="38"/>
-    <tableColumn id="58" xr3:uid="{586E5BDF-4F57-420B-894C-52DDFEFB3768}" name="Atributo_x000d__x000a_Ángulo máximo de apertura" dataDxfId="37"/>
-    <tableColumn id="59" xr3:uid="{DD0CEF83-8BB0-41B1-8AA5-E48C50B69D6E}" name="Atributo_x000d__x000a_Incluye herrajes de montaje" dataDxfId="36"/>
-    <tableColumn id="60" xr3:uid="{6003663E-0EE5-4EA9-AFB8-1AAF3DC769E4}" name="Atributo_x000d__x000a_Cantidad de agujeros de montaje" dataDxfId="35"/>
-    <tableColumn id="61" xr3:uid="{C94BBFDE-2D22-4FD9-B198-4299734F8A16}" name="Atributo_x000d__x000a_Material" dataDxfId="34"/>
-    <tableColumn id="62" xr3:uid="{8CB1E75D-17F7-4D3B-87E7-93E5C31EE4B5}" name="Atributo_x000d__x000a_Diámetro interior" dataDxfId="33"/>
-    <tableColumn id="63" xr3:uid="{059FEC74-F32D-42E7-B27C-E67B315105C9}" name="Atributo_x000d__x000a_Diámetro externo" dataDxfId="32"/>
-    <tableColumn id="64" xr3:uid="{5F2838F4-BC86-4693-84B3-EE36CEF8CE6D}" name="Atributo_x000d__x000a_Espesor" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{E0B87E46-8A56-47D2-BAE9-4BCB2D23A35F}" name="Descripción" dataDxfId="56"/>
+    <tableColumn id="9" xr3:uid="{F4376C87-095C-4FB9-BEFB-D97C5942E3DD}" name="Precio" dataDxfId="55"/>
+    <tableColumn id="10" xr3:uid="{2851AC63-AA68-40EF-AC01-B1CB63CB3F54}" name="Moneda" dataDxfId="54"/>
+    <tableColumn id="11" xr3:uid="{9A486920-D334-49F4-9651-3544B340B8F7}" name="SKU" dataDxfId="53"/>
+    <tableColumn id="12" xr3:uid="{504E12D6-4FFA-4E63-988B-D8351618F850}" name="Estado" dataDxfId="52"/>
+    <tableColumn id="13" xr3:uid="{8C530989-E33E-4C51-BB2A-A69301EA5973}" name="Stock" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{B8F4AAD6-AFC8-453A-BEA4-C8315EA4E074}" name="Tipo de Publicación" dataDxfId="50"/>
+    <tableColumn id="15" xr3:uid="{D515DD2D-9950-499C-A3C9-02EAB564CDB6}" name="Condición" dataDxfId="49"/>
+    <tableColumn id="16" xr3:uid="{D304FA7B-1DB5-467C-B4C0-159C7B76ED81}" name="Envio Gratis" dataDxfId="48"/>
+    <tableColumn id="17" xr3:uid="{4FABBCF4-6194-4782-B178-8C992F5A9BF7}" name="Precio Envio Gratis" dataDxfId="47"/>
+    <tableColumn id="18" xr3:uid="{98934760-3BF6-4D2B-BEE7-A1649AD0AE03}" name="Modo Envio" dataDxfId="46"/>
+    <tableColumn id="19" xr3:uid="{09015D66-D40E-48FC-AA0D-DF7C960CED1C}" name="Metodo Envio" dataDxfId="45"/>
+    <tableColumn id="20" xr3:uid="{74BB07AA-3E72-4250-A57F-C6B07358395F}" name="Retira en Persona" dataDxfId="44"/>
+    <tableColumn id="21" xr3:uid="{9AF8BAC3-B650-4C3D-AF7D-94AD638CD8D1}" name="Envio FLEX" dataDxfId="43"/>
+    <tableColumn id="22" xr3:uid="{D6EDAE76-DF30-4549-8156-D06F228C6AE8}" name="Garantia" dataDxfId="42"/>
+    <tableColumn id="23" xr3:uid="{CA3CB06E-FF35-4B00-8F1F-BE67BBA7A61A}" name="Fecha Creación" dataDxfId="41"/>
+    <tableColumn id="24" xr3:uid="{B9179D59-0B0B-47E5-84C3-450FA1E054DF}" name="Última Actualización" dataDxfId="40"/>
+    <tableColumn id="25" xr3:uid="{35DCB46A-158D-403D-818B-8CBB83F35F5A}" name="Resultado" dataDxfId="39"/>
+    <tableColumn id="26" xr3:uid="{51193C13-B5C6-4AB0-AD61-2582ADED050F}" name="Resultado Observaciones" dataDxfId="38"/>
+    <tableColumn id="27" xr3:uid="{592AE190-9BCD-4633-A51D-AB6AA482AB93}" name="Imagen 1" dataDxfId="37"/>
+    <tableColumn id="28" xr3:uid="{5BCBA99F-8D2E-4EC0-9BC4-CEC88F1CDA88}" name="Imagen 2" dataDxfId="36"/>
+    <tableColumn id="29" xr3:uid="{1DA8AC64-0DDB-4549-828F-B7AAA646A393}" name="Imagen 3" dataDxfId="35"/>
+    <tableColumn id="30" xr3:uid="{E3E11581-3A67-491F-B299-4FA96F0CA2BB}" name="Imagen 4" dataDxfId="34"/>
+    <tableColumn id="31" xr3:uid="{3E72739F-F6D5-413E-A939-3776645507BD}" name="Imagen 5" dataDxfId="33"/>
+    <tableColumn id="32" xr3:uid="{A85C7D82-6155-4554-9B3D-18ED31E78966}" name="Imagen 6" dataDxfId="32"/>
+    <tableColumn id="33" xr3:uid="{DE5CDDDB-F9AD-43F1-9476-B132B7023807}" name="Imagen 7" dataDxfId="31"/>
+    <tableColumn id="34" xr3:uid="{68CE6975-FAB8-4236-8F39-1AA4B658E504}" name="Imagen 8" dataDxfId="30"/>
+    <tableColumn id="35" xr3:uid="{176F89D3-55C1-4864-A9EE-83C429B15147}" name="Imagen 9" dataDxfId="29"/>
+    <tableColumn id="36" xr3:uid="{822D9C27-446E-4C51-834D-EFA6235C1FD1}" name="Imagen 10" dataDxfId="28"/>
+    <tableColumn id="37" xr3:uid="{06003688-CF66-40B9-80A3-0E817EF58334}" name="Visitas" dataDxfId="27"/>
+    <tableColumn id="38" xr3:uid="{867443DD-E155-463F-8AB6-127CAC8F04D7}" name="Vendidos" dataDxfId="26"/>
+    <tableColumn id="39" xr3:uid="{450CCE7E-504E-43B5-996D-68A045978B20}" name="Fecha Ultima Venta" dataDxfId="25"/>
+    <tableColumn id="40" xr3:uid="{F045B770-A77E-4B81-B2C3-B8805902967A}" name="Variación_x000d__x000a_Color" dataDxfId="24"/>
+    <tableColumn id="41" xr3:uid="{1B5F14A3-3B98-4C46-A40D-D6B6D3A92694}" name="Variación_x000d__x000a_Código universal de producto" dataDxfId="23"/>
+    <tableColumn id="42" xr3:uid="{46FC1A21-3FAC-4529-89E5-671FB1C585CF}" name="Variación_x000d__x000a_Código OEM" dataDxfId="22"/>
+    <tableColumn id="43" xr3:uid="{B0BD1BC7-A155-4C36-9BFA-6134205BF2C2}" name="Atributo_x000d__x000a_Marca" dataDxfId="21"/>
+    <tableColumn id="44" xr3:uid="{7DFE1A7F-BFBA-4B08-A268-9FA639E80D6D}" name="Atributo_x000d__x000a_Número de pieza" dataDxfId="20"/>
+    <tableColumn id="45" xr3:uid="{C81DC53D-A59A-4BE3-85CB-7E330249E5A3}" name="Atributo_x000d__x000a_Modelo" dataDxfId="19"/>
+    <tableColumn id="46" xr3:uid="{17D22998-DBB8-4832-B2F1-0651FF94B680}" name="Atributo_x000d__x000a_Formato de venta" dataDxfId="18"/>
+    <tableColumn id="47" xr3:uid="{D119AEAD-E9A2-4AC9-BB22-A998D88D0BA7}" name="Atributo_x000d__x000a_Unidades por pack" dataDxfId="17"/>
+    <tableColumn id="48" xr3:uid="{16708B52-94B7-4A28-8034-BF5B173D0A22}" name="Atributo_x000d__x000a_Largo extendido" dataDxfId="16"/>
+    <tableColumn id="49" xr3:uid="{67FDACCE-02CC-47CE-BC26-2CCAD33D28DF}" name="Atributo_x000d__x000a_Largo comprimido" dataDxfId="15"/>
+    <tableColumn id="50" xr3:uid="{4C316B6B-2322-4B67-9371-CEFB9BF5BC1E}" name="Atributo_x000d__x000a_Lugar de colocación" dataDxfId="14"/>
+    <tableColumn id="51" xr3:uid="{B7C39FD4-4950-4A18-B31E-65EA4E00CCB0}" name="Atributo_x000d__x000a_Origen" dataDxfId="13"/>
+    <tableColumn id="52" xr3:uid="{4750DCC5-91A5-4023-8D76-2FABC2DB19D1}" name="Atributo_x000d__x000a_Tipo de vehículo" dataDxfId="12"/>
+    <tableColumn id="53" xr3:uid="{311F8834-A35A-421E-9403-BC70515A42D0}" name="Atributo_x000d__x000a_Código universal de producto" dataDxfId="11"/>
+    <tableColumn id="54" xr3:uid="{A6B39D83-4E6C-473C-AF8F-03D5F386FB74}" name="Atributo_x000d__x000a_Código OEM" dataDxfId="10"/>
+    <tableColumn id="55" xr3:uid="{D281CDC7-FACC-4E01-AB6B-7D3FBC5D4615}" name="Atributo_x000d__x000a_Motivo de GTIN vacío" dataDxfId="9"/>
+    <tableColumn id="56" xr3:uid="{3345F854-C43F-427B-BADA-ACF763FA14DB}" name="Atributo_x000d__x000a_Material del núcleo" dataDxfId="8"/>
+    <tableColumn id="57" xr3:uid="{D181DC2A-403B-4CA6-9E8A-872ED1FD375B}" name="Atributo_x000d__x000a_Cantidad de llaves" dataDxfId="7"/>
+    <tableColumn id="58" xr3:uid="{586E5BDF-4F57-420B-894C-52DDFEFB3768}" name="Atributo_x000d__x000a_Ángulo máximo de apertura" dataDxfId="6"/>
+    <tableColumn id="59" xr3:uid="{DD0CEF83-8BB0-41B1-8AA5-E48C50B69D6E}" name="Atributo_x000d__x000a_Incluye herrajes de montaje" dataDxfId="5"/>
+    <tableColumn id="60" xr3:uid="{6003663E-0EE5-4EA9-AFB8-1AAF3DC769E4}" name="Atributo_x000d__x000a_Cantidad de agujeros de montaje" dataDxfId="4"/>
+    <tableColumn id="61" xr3:uid="{C94BBFDE-2D22-4FD9-B198-4299734F8A16}" name="Atributo_x000d__x000a_Material" dataDxfId="3"/>
+    <tableColumn id="62" xr3:uid="{8CB1E75D-17F7-4D3B-87E7-93E5C31EE4B5}" name="Atributo_x000d__x000a_Diámetro interior" dataDxfId="2"/>
+    <tableColumn id="63" xr3:uid="{059FEC74-F32D-42E7-B27C-E67B315105C9}" name="Atributo_x000d__x000a_Diámetro externo" dataDxfId="1"/>
+    <tableColumn id="64" xr3:uid="{5F2838F4-BC86-4693-84B3-EE36CEF8CE6D}" name="Atributo_x000d__x000a_Espesor" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4178,7 +4178,7 @@
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="15.28515625" customWidth="1"/>
     <col min="4" max="4" width="50.7109375" customWidth="1"/>
-    <col min="5" max="5" width="40.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" customWidth="1"/>
     <col min="6" max="6" width="69.7109375" customWidth="1"/>
     <col min="7" max="7" width="7.7109375" customWidth="1"/>
     <col min="8" max="8" width="80.7109375" customWidth="1"/>
@@ -4423,39 +4423,39 @@
         <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="L2" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M2" s="2">
         <v>0</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q2" s="17"/>
       <c r="R2" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S2" s="2"/>
       <c r="T2" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W2" s="20">
         <v>45611.821261574078</v>
@@ -4466,7 +4466,7 @@
       <c r="Y2" s="21"/>
       <c r="Z2" s="15"/>
       <c r="AA2" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
@@ -4488,41 +4488,41 @@
       <c r="AO2" s="24"/>
       <c r="AP2" s="2"/>
       <c r="AQ2" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR2" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AS2" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AT2" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU2" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU2" s="6" t="s">
+      <c r="AV2" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="AV2" s="6" t="s">
-        <v>294</v>
-      </c>
       <c r="AW2" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AX2" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AY2" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ2" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA2" s="23"/>
       <c r="BB2" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC2" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD2" s="2"/>
       <c r="BE2" s="2"/>
@@ -4562,39 +4562,39 @@
         <v>15</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M3" s="2">
         <v>0</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q3" s="17"/>
       <c r="R3" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S3" s="2"/>
       <c r="T3" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W3" s="20">
         <v>45611.821388888886</v>
@@ -4605,7 +4605,7 @@
       <c r="Y3" s="21"/>
       <c r="Z3" s="15"/>
       <c r="AA3" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
@@ -4627,37 +4627,37 @@
       <c r="AO3" s="24"/>
       <c r="AP3" s="2"/>
       <c r="AQ3" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR3" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AS3" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AT3" s="6"/>
       <c r="AU3" s="6"/>
       <c r="AV3" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AW3" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AX3" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AY3" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ3" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA3" s="23"/>
       <c r="BB3" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC3" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD3" s="2"/>
       <c r="BE3" s="2"/>
@@ -4697,39 +4697,39 @@
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M4" s="2">
         <v>0</v>
       </c>
       <c r="N4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q4" s="17"/>
       <c r="R4" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V4" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W4" s="20">
         <v>45611.821331018517</v>
@@ -4740,7 +4740,7 @@
       <c r="Y4" s="21"/>
       <c r="Z4" s="15"/>
       <c r="AA4" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AB4" s="2"/>
       <c r="AC4" s="2"/>
@@ -4762,41 +4762,41 @@
       <c r="AO4" s="24"/>
       <c r="AP4" s="2"/>
       <c r="AQ4" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR4" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AS4" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AT4" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU4" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU4" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV4" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AW4" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AX4" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AY4" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ4" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA4" s="23"/>
       <c r="BB4" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC4" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD4" s="2"/>
       <c r="BE4" s="2"/>
@@ -4830,45 +4830,45 @@
         <v>43</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>140</v>
+        <v>349</v>
       </c>
       <c r="I5" s="17">
         <v>12</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M5" s="2">
         <v>1</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S5" s="2"/>
       <c r="T5" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U5" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W5" s="20">
         <v>45611.820868055554</v>
@@ -4879,7 +4879,7 @@
       <c r="Y5" s="21"/>
       <c r="Z5" s="15"/>
       <c r="AA5" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
@@ -4901,41 +4901,41 @@
       <c r="AO5" s="24"/>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR5" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AS5" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AT5" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU5" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU5" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV5" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AW5" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AX5" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AY5" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ5" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA5" s="23"/>
       <c r="BB5" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC5" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2"/>
@@ -4969,45 +4969,45 @@
         <v>46</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I6" s="17">
         <v>12</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M6" s="2">
         <v>0</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q6" s="17"/>
       <c r="R6" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S6" s="2"/>
       <c r="T6" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U6" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W6" s="20">
         <v>45611.820937500001</v>
@@ -5018,7 +5018,7 @@
       <c r="Y6" s="21"/>
       <c r="Z6" s="15"/>
       <c r="AA6" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AB6" s="2"/>
       <c r="AC6" s="2"/>
@@ -5040,41 +5040,41 @@
       <c r="AO6" s="24"/>
       <c r="AP6" s="2"/>
       <c r="AQ6" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR6" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AS6" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AT6" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU6" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU6" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV6" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AW6" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AX6" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY6" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ6" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA6" s="23"/>
       <c r="BB6" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC6" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD6" s="2"/>
       <c r="BE6" s="2"/>
@@ -5108,45 +5108,45 @@
         <v>55</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I7" s="17">
         <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M7" s="2">
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q7" s="17"/>
       <c r="R7" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S7" s="2"/>
       <c r="T7" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W7" s="20">
         <v>45611.821643518517</v>
@@ -5157,7 +5157,7 @@
       <c r="Y7" s="21"/>
       <c r="Z7" s="15"/>
       <c r="AA7" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
@@ -5179,41 +5179,41 @@
       <c r="AO7" s="24"/>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR7" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AS7" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AT7" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU7" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU7" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV7" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AW7" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AX7" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY7" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ7" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA7" s="23"/>
       <c r="BB7" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC7" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD7" s="2"/>
       <c r="BE7" s="2"/>
@@ -5247,45 +5247,45 @@
         <v>38</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I8" s="17">
         <v>13</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M8" s="2">
         <v>0</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q8" s="17"/>
       <c r="R8" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S8" s="2"/>
       <c r="T8" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W8" s="20">
         <v>45611.820856481485</v>
@@ -5296,7 +5296,7 @@
       <c r="Y8" s="21"/>
       <c r="Z8" s="15"/>
       <c r="AA8" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AB8" s="2"/>
       <c r="AC8" s="2"/>
@@ -5318,41 +5318,41 @@
       <c r="AO8" s="24"/>
       <c r="AP8" s="2"/>
       <c r="AQ8" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR8" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AS8" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AT8" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU8" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU8" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV8" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AW8" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AX8" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AY8" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ8" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA8" s="23"/>
       <c r="BB8" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC8" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD8" s="2"/>
       <c r="BE8" s="2"/>
@@ -5386,45 +5386,45 @@
         <v>49</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I9" s="17">
         <v>15</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M9" s="2">
         <v>0</v>
       </c>
       <c r="N9" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q9" s="17"/>
       <c r="R9" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S9" s="2"/>
       <c r="T9" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U9" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W9" s="20">
         <v>45611.821319444447</v>
@@ -5435,7 +5435,7 @@
       <c r="Y9" s="21"/>
       <c r="Z9" s="15"/>
       <c r="AA9" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AB9" s="2"/>
       <c r="AC9" s="2"/>
@@ -5457,41 +5457,41 @@
       <c r="AO9" s="24"/>
       <c r="AP9" s="2"/>
       <c r="AQ9" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR9" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AS9" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AT9" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU9" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU9" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV9" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AW9" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AX9" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AY9" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ9" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA9" s="23"/>
       <c r="BB9" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC9" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD9" s="2"/>
       <c r="BE9" s="2"/>
@@ -5525,45 +5525,45 @@
         <v>36</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I10" s="17">
         <v>17.5</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M10" s="2">
         <v>0</v>
       </c>
       <c r="N10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q10" s="17"/>
       <c r="R10" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S10" s="2"/>
       <c r="T10" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U10" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V10" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W10" s="20">
         <v>45611.821111111109</v>
@@ -5574,7 +5574,7 @@
       <c r="Y10" s="21"/>
       <c r="Z10" s="15"/>
       <c r="AA10" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AB10" s="2"/>
       <c r="AC10" s="2"/>
@@ -5596,37 +5596,37 @@
       <c r="AO10" s="24"/>
       <c r="AP10" s="2"/>
       <c r="AQ10" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR10" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AS10" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AT10" s="6"/>
       <c r="AU10" s="6"/>
       <c r="AV10" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AW10" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AX10" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY10" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ10" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA10" s="23"/>
       <c r="BB10" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC10" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD10" s="2"/>
       <c r="BE10" s="2"/>
@@ -5660,45 +5660,45 @@
         <v>41</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I11" s="17">
         <v>20</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M11" s="2">
         <v>0</v>
       </c>
       <c r="N11" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q11" s="17"/>
       <c r="R11" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S11" s="2"/>
       <c r="T11" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U11" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W11" s="20">
         <v>45611.821145833332</v>
@@ -5709,7 +5709,7 @@
       <c r="Y11" s="21"/>
       <c r="Z11" s="15"/>
       <c r="AA11" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AB11" s="2"/>
       <c r="AC11" s="2"/>
@@ -5731,41 +5731,41 @@
       <c r="AO11" s="24"/>
       <c r="AP11" s="2"/>
       <c r="AQ11" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR11" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AS11" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AT11" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU11" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU11" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV11" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AW11" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AX11" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY11" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ11" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA11" s="23"/>
       <c r="BB11" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC11" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD11" s="2"/>
       <c r="BE11" s="2"/>
@@ -5799,45 +5799,45 @@
         <v>52</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I12" s="17">
         <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M12" s="2">
         <v>0</v>
       </c>
       <c r="N12" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="P12" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q12" s="17"/>
       <c r="R12" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S12" s="2"/>
       <c r="T12" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U12" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V12" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W12" s="20">
         <v>45611.821435185186</v>
@@ -5848,7 +5848,7 @@
       <c r="Y12" s="21"/>
       <c r="Z12" s="15"/>
       <c r="AA12" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AB12" s="2"/>
       <c r="AC12" s="2"/>
@@ -5870,37 +5870,37 @@
       <c r="AO12" s="24"/>
       <c r="AP12" s="2"/>
       <c r="AQ12" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR12" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AS12" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AT12" s="6"/>
       <c r="AU12" s="6"/>
       <c r="AV12" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AW12" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AX12" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AY12" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ12" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA12" s="23"/>
       <c r="BB12" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC12" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD12" s="2"/>
       <c r="BE12" s="2"/>
@@ -5934,45 +5934,45 @@
         <v>54</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I13" s="17">
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M13" s="2">
         <v>0</v>
       </c>
       <c r="N13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O13" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q13" s="17"/>
       <c r="R13" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S13" s="2"/>
       <c r="T13" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U13" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V13" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W13" s="20">
         <v>45611.821608796294</v>
@@ -5983,7 +5983,7 @@
       <c r="Y13" s="21"/>
       <c r="Z13" s="15"/>
       <c r="AA13" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AB13" s="2"/>
       <c r="AC13" s="2"/>
@@ -6005,41 +6005,41 @@
       <c r="AO13" s="24"/>
       <c r="AP13" s="2"/>
       <c r="AQ13" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR13" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AS13" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AT13" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU13" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU13" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV13" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AW13" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AX13" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY13" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ13" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA13" s="23"/>
       <c r="BB13" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC13" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD13" s="2"/>
       <c r="BE13" s="2"/>
@@ -6073,45 +6073,45 @@
         <v>59</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I14" s="17">
         <v>15</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M14" s="2">
         <v>0</v>
       </c>
       <c r="N14" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O14" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="P14" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q14" s="17"/>
       <c r="R14" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S14" s="2"/>
       <c r="T14" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U14" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V14" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W14" s="20">
         <v>45611.820798611108</v>
@@ -6122,10 +6122,10 @@
       <c r="Y14" s="21"/>
       <c r="Z14" s="15"/>
       <c r="AA14" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" s="2"/>
@@ -6146,39 +6146,39 @@
       <c r="AO14" s="24"/>
       <c r="AP14" s="2"/>
       <c r="AQ14" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR14" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AS14" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AT14" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU14" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU14" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV14" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AW14" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AX14" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY14" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ14" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA14" s="23"/>
       <c r="BB14" s="6"/>
       <c r="BC14" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD14" s="2"/>
       <c r="BE14" s="2"/>
@@ -6212,45 +6212,45 @@
         <v>49</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I15" s="17">
         <v>16</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M15" s="2">
         <v>0</v>
       </c>
       <c r="N15" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O15" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q15" s="17"/>
       <c r="R15" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S15" s="2"/>
       <c r="T15" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V15" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W15" s="20">
         <v>45611.821435185186</v>
@@ -6261,7 +6261,7 @@
       <c r="Y15" s="21"/>
       <c r="Z15" s="15"/>
       <c r="AA15" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AB15" s="2"/>
       <c r="AC15" s="2"/>
@@ -6283,41 +6283,41 @@
       <c r="AO15" s="24"/>
       <c r="AP15" s="2"/>
       <c r="AQ15" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR15" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AS15" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AT15" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU15" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU15" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV15" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AW15" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AX15" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AY15" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ15" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA15" s="23"/>
       <c r="BB15" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC15" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD15" s="2"/>
       <c r="BE15" s="2"/>
@@ -6351,45 +6351,45 @@
         <v>55</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I16" s="17">
         <v>15</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M16" s="2">
         <v>0</v>
       </c>
       <c r="N16" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O16" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="P16" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q16" s="17"/>
       <c r="R16" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S16" s="2"/>
       <c r="T16" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U16" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W16" s="20">
         <v>45611.820416666669</v>
@@ -6400,7 +6400,7 @@
       <c r="Y16" s="21"/>
       <c r="Z16" s="15"/>
       <c r="AA16" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AB16" s="2"/>
       <c r="AC16" s="2"/>
@@ -6422,39 +6422,39 @@
       <c r="AO16" s="24"/>
       <c r="AP16" s="2"/>
       <c r="AQ16" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR16" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AS16" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AT16" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU16" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU16" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV16" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AW16" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AX16" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY16" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ16" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA16" s="23"/>
       <c r="BB16" s="6"/>
       <c r="BC16" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD16" s="2"/>
       <c r="BE16" s="2"/>
@@ -6488,45 +6488,45 @@
         <v>58</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I17" s="17">
         <v>8</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M17" s="2">
         <v>0</v>
       </c>
       <c r="N17" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O17" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="P17" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q17" s="17"/>
       <c r="R17" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S17" s="2"/>
       <c r="T17" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U17" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V17" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W17" s="20">
         <v>45611.824097222219</v>
@@ -6537,7 +6537,7 @@
       <c r="Y17" s="21"/>
       <c r="Z17" s="15"/>
       <c r="AA17" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
@@ -6559,13 +6559,13 @@
       <c r="AO17" s="24"/>
       <c r="AP17" s="2"/>
       <c r="AQ17" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AR17" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AS17" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AT17" s="6"/>
       <c r="AU17" s="6"/>
@@ -6574,12 +6574,12 @@
       <c r="AX17" s="6"/>
       <c r="AY17" s="6"/>
       <c r="AZ17" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA17" s="23"/>
       <c r="BB17" s="6"/>
       <c r="BC17" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="BD17" s="2"/>
       <c r="BE17" s="2"/>
@@ -6613,45 +6613,45 @@
         <v>56</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I18" s="17">
         <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M18" s="2">
         <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O18" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O18" s="2" t="s">
+      <c r="P18" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q18" s="17"/>
       <c r="R18" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S18" s="2"/>
       <c r="T18" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U18" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V18" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W18" s="20">
         <v>45611.820474537039</v>
@@ -6662,7 +6662,7 @@
       <c r="Y18" s="21"/>
       <c r="Z18" s="15"/>
       <c r="AA18" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AB18" s="2"/>
       <c r="AC18" s="2"/>
@@ -6684,39 +6684,39 @@
       <c r="AO18" s="24"/>
       <c r="AP18" s="2"/>
       <c r="AQ18" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR18" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AS18" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AT18" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU18" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU18" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV18" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AW18" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AX18" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AY18" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ18" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA18" s="23"/>
       <c r="BB18" s="6"/>
       <c r="BC18" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD18" s="2"/>
       <c r="BE18" s="2"/>
@@ -6750,45 +6750,45 @@
         <v>33</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I19" s="17">
         <v>12</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M19" s="2">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O19" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O19" s="2" t="s">
+      <c r="P19" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q19" s="17"/>
       <c r="R19" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S19" s="2"/>
       <c r="T19" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U19" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V19" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W19" s="20">
         <v>45611.820925925924</v>
@@ -6799,7 +6799,7 @@
       <c r="Y19" s="21"/>
       <c r="Z19" s="15"/>
       <c r="AA19" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AB19" s="2"/>
       <c r="AC19" s="2"/>
@@ -6821,41 +6821,41 @@
       <c r="AO19" s="24"/>
       <c r="AP19" s="2"/>
       <c r="AQ19" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR19" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AS19" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AT19" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU19" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU19" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV19" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AW19" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AX19" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AY19" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ19" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA19" s="23"/>
       <c r="BB19" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC19" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD19" s="2"/>
       <c r="BE19" s="2"/>
@@ -6889,45 +6889,45 @@
         <v>49</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I20" s="17">
         <v>20</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M20" s="2">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="P20" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q20" s="17"/>
       <c r="R20" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S20" s="2"/>
       <c r="T20" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U20" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V20" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W20" s="20">
         <v>45611.821192129632</v>
@@ -6938,7 +6938,7 @@
       <c r="Y20" s="21"/>
       <c r="Z20" s="15"/>
       <c r="AA20" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
@@ -6960,41 +6960,41 @@
       <c r="AO20" s="24"/>
       <c r="AP20" s="2"/>
       <c r="AQ20" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR20" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AS20" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AT20" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU20" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU20" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV20" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AW20" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AX20" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="AY20" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="AY20" s="6" t="s">
-        <v>342</v>
-      </c>
       <c r="AZ20" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA20" s="23"/>
       <c r="BB20" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC20" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD20" s="2"/>
       <c r="BE20" s="2"/>
@@ -7028,45 +7028,45 @@
         <v>49</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I21" s="17">
         <v>20</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M21" s="2">
         <v>0</v>
       </c>
       <c r="N21" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="P21" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q21" s="17"/>
       <c r="R21" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S21" s="2"/>
       <c r="T21" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U21" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V21" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W21" s="20">
         <v>45611.821215277778</v>
@@ -7077,7 +7077,7 @@
       <c r="Y21" s="21"/>
       <c r="Z21" s="15"/>
       <c r="AA21" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AB21" s="2"/>
       <c r="AC21" s="2"/>
@@ -7099,41 +7099,41 @@
       <c r="AO21" s="24"/>
       <c r="AP21" s="2"/>
       <c r="AQ21" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR21" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AS21" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AT21" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU21" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU21" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV21" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AW21" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AX21" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AY21" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ21" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA21" s="23"/>
       <c r="BB21" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC21" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD21" s="2"/>
       <c r="BE21" s="2"/>
@@ -7167,45 +7167,45 @@
         <v>45</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I22" s="17">
         <v>18</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
       </c>
       <c r="N22" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="P22" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q22" s="17"/>
       <c r="R22" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S22" s="2"/>
       <c r="T22" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U22" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V22" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W22" s="20">
         <v>45611.821296296293</v>
@@ -7216,7 +7216,7 @@
       <c r="Y22" s="21"/>
       <c r="Z22" s="15"/>
       <c r="AA22" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AB22" s="2"/>
       <c r="AC22" s="2"/>
@@ -7238,41 +7238,41 @@
       <c r="AO22" s="24"/>
       <c r="AP22" s="2"/>
       <c r="AQ22" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR22" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AS22" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AT22" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU22" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU22" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV22" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AW22" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AX22" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AY22" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ22" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA22" s="23"/>
       <c r="BB22" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC22" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD22" s="2"/>
       <c r="BE22" s="2"/>
@@ -7310,39 +7310,39 @@
         <v>15</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
       </c>
       <c r="N23" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O23" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="P23" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q23" s="17"/>
       <c r="R23" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S23" s="2"/>
       <c r="T23" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U23" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V23" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W23" s="20">
         <v>45611.824074074073</v>
@@ -7353,7 +7353,7 @@
       <c r="Y23" s="21"/>
       <c r="Z23" s="15"/>
       <c r="AA23" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AB23" s="2"/>
       <c r="AC23" s="2"/>
@@ -7375,41 +7375,41 @@
       <c r="AO23" s="24"/>
       <c r="AP23" s="2"/>
       <c r="AQ23" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR23" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AS23" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AT23" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU23" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU23" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV23" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AW23" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AX23" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AY23" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ23" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA23" s="23"/>
       <c r="BB23" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC23" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD23" s="2"/>
       <c r="BE23" s="2"/>
@@ -7443,45 +7443,45 @@
         <v>59</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I24" s="17">
         <v>20</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M24" s="2">
         <v>0</v>
       </c>
       <c r="N24" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O24" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O24" s="2" t="s">
+      <c r="P24" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q24" s="17"/>
       <c r="R24" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S24" s="2"/>
       <c r="T24" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U24" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V24" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W24" s="20">
         <v>45611.820462962962</v>
@@ -7492,7 +7492,7 @@
       <c r="Y24" s="21"/>
       <c r="Z24" s="15"/>
       <c r="AA24" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AB24" s="2"/>
       <c r="AC24" s="2"/>
@@ -7514,37 +7514,37 @@
       <c r="AO24" s="24"/>
       <c r="AP24" s="2"/>
       <c r="AQ24" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR24" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AS24" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AT24" s="6"/>
       <c r="AU24" s="6"/>
       <c r="AV24" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AW24" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AX24" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY24" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ24" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA24" s="23"/>
       <c r="BB24" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC24" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD24" s="2"/>
       <c r="BE24" s="2"/>
@@ -7578,45 +7578,45 @@
         <v>52</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I25" s="17">
         <v>16</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M25" s="2">
         <v>0</v>
       </c>
       <c r="N25" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O25" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="P25" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q25" s="17"/>
       <c r="R25" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S25" s="2"/>
       <c r="T25" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U25" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V25" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W25" s="20">
         <v>45611.820497685185</v>
@@ -7627,7 +7627,7 @@
       <c r="Y25" s="21"/>
       <c r="Z25" s="15"/>
       <c r="AA25" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AB25" s="2"/>
       <c r="AC25" s="2"/>
@@ -7649,41 +7649,41 @@
       <c r="AO25" s="24"/>
       <c r="AP25" s="2"/>
       <c r="AQ25" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR25" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AS25" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AT25" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU25" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU25" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV25" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AW25" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AX25" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AY25" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ25" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA25" s="23"/>
       <c r="BB25" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC25" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD25" s="2"/>
       <c r="BE25" s="2"/>
@@ -7717,45 +7717,45 @@
         <v>51</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I26" s="17">
         <v>14</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M26" s="2">
         <v>0</v>
       </c>
       <c r="N26" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O26" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O26" s="2" t="s">
+      <c r="P26" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q26" s="17"/>
       <c r="R26" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S26" s="2"/>
       <c r="T26" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U26" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V26" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W26" s="20">
         <v>45611.821122685185</v>
@@ -7766,7 +7766,7 @@
       <c r="Y26" s="21"/>
       <c r="Z26" s="15"/>
       <c r="AA26" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
@@ -7788,41 +7788,41 @@
       <c r="AO26" s="24"/>
       <c r="AP26" s="2"/>
       <c r="AQ26" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR26" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AS26" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AT26" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AU26" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU26" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV26" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AW26" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AX26" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AY26" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AZ26" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA26" s="23"/>
       <c r="BB26" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC26" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD26" s="2"/>
       <c r="BE26" s="2"/>
@@ -7856,45 +7856,45 @@
         <v>56</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I27" s="17">
         <v>15</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M27" s="2">
         <v>0</v>
       </c>
       <c r="N27" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O27" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O27" s="2" t="s">
+      <c r="P27" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q27" s="17"/>
       <c r="R27" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S27" s="2"/>
       <c r="T27" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U27" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="V27" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="W27" s="20">
         <v>45611.821284722224</v>
@@ -7905,7 +7905,7 @@
       <c r="Y27" s="21"/>
       <c r="Z27" s="15"/>
       <c r="AA27" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AB27" s="2"/>
       <c r="AC27" s="2"/>
@@ -7927,41 +7927,41 @@
       <c r="AO27" s="24"/>
       <c r="AP27" s="2"/>
       <c r="AQ27" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AR27" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AS27" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="AT27" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="AT27" s="6" t="s">
+      <c r="AU27" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="AU27" s="6" t="s">
-        <v>293</v>
-      </c>
       <c r="AV27" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AW27" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="AX27" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="AX27" s="6" t="s">
-        <v>335</v>
-      </c>
       <c r="AY27" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AZ27" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA27" s="23"/>
       <c r="BB27" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="BC27" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="BD27" s="2"/>
       <c r="BE27" s="2"/>
@@ -7995,45 +7995,45 @@
         <v>55</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I28" s="17">
         <v>9.86</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M28" s="2">
         <v>0</v>
       </c>
       <c r="N28" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O28" s="2" t="s">
+      <c r="P28" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q28" s="17"/>
       <c r="R28" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S28" s="2"/>
       <c r="T28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W28" s="20">
         <v>45665.490914351853</v>
@@ -8044,13 +8044,13 @@
       <c r="Y28" s="21"/>
       <c r="Z28" s="15"/>
       <c r="AA28" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AC28" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AD28" s="2"/>
       <c r="AE28" s="2"/>
@@ -8070,10 +8070,10 @@
       <c r="AO28" s="25"/>
       <c r="AP28" s="9"/>
       <c r="AQ28" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AR28" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
@@ -8082,14 +8082,14 @@
       <c r="AW28" s="2"/>
       <c r="AX28" s="2"/>
       <c r="AY28" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AZ28" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="AZ28" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="BA28" s="24"/>
       <c r="BB28" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="BC28" s="7"/>
       <c r="BD28" s="6"/>
@@ -8124,45 +8124,45 @@
         <v>49</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I29" s="17">
         <v>9.86</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M29" s="2">
         <v>0</v>
       </c>
       <c r="N29" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q29" s="17"/>
       <c r="R29" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S29" s="2"/>
       <c r="T29" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W29" s="20">
         <v>45665.490937499999</v>
@@ -8173,16 +8173,16 @@
       <c r="Y29" s="21"/>
       <c r="Z29" s="15"/>
       <c r="AA29" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AD29" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AE29" s="2"/>
       <c r="AF29" s="2"/>
@@ -8201,10 +8201,10 @@
       <c r="AO29" s="25"/>
       <c r="AP29" s="9"/>
       <c r="AQ29" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AR29" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
@@ -8213,14 +8213,14 @@
       <c r="AW29" s="2"/>
       <c r="AX29" s="2"/>
       <c r="AY29" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AZ29" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="AZ29" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="BA29" s="24"/>
       <c r="BB29" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="BC29" s="7"/>
       <c r="BD29" s="6"/>
@@ -8255,45 +8255,45 @@
         <v>54</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I30" s="17">
         <v>9.86</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M30" s="2">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O30" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="P30" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q30" s="17"/>
       <c r="R30" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S30" s="2"/>
       <c r="T30" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W30" s="20">
         <v>45665.490914351853</v>
@@ -8304,16 +8304,16 @@
       <c r="Y30" s="21"/>
       <c r="Z30" s="15"/>
       <c r="AA30" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AB30" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AC30" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AD30" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AE30" s="2"/>
       <c r="AF30" s="2"/>
@@ -8332,10 +8332,10 @@
       <c r="AO30" s="25"/>
       <c r="AP30" s="9"/>
       <c r="AQ30" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AR30" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
@@ -8344,14 +8344,14 @@
       <c r="AW30" s="2"/>
       <c r="AX30" s="2"/>
       <c r="AY30" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AZ30" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="AZ30" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="BA30" s="24"/>
       <c r="BB30" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="BC30" s="7"/>
       <c r="BD30" s="6"/>
@@ -8386,45 +8386,45 @@
         <v>42</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I31" s="17">
         <v>9.86</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M31" s="2">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O31" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O31" s="2" t="s">
+      <c r="P31" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q31" s="17"/>
       <c r="R31" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S31" s="2"/>
       <c r="T31" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W31" s="20">
         <v>45665.490613425929</v>
@@ -8435,13 +8435,13 @@
       <c r="Y31" s="21"/>
       <c r="Z31" s="15"/>
       <c r="AA31" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AB31" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AC31" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AD31" s="2"/>
       <c r="AE31" s="2"/>
@@ -8461,10 +8461,10 @@
       <c r="AO31" s="25"/>
       <c r="AP31" s="9"/>
       <c r="AQ31" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AR31" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
@@ -8473,14 +8473,14 @@
       <c r="AW31" s="2"/>
       <c r="AX31" s="2"/>
       <c r="AY31" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AZ31" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="AZ31" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="BA31" s="24"/>
       <c r="BB31" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="BC31" s="7"/>
       <c r="BD31" s="6"/>
@@ -8515,45 +8515,45 @@
         <v>56</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I32" s="17">
         <v>9.86</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M32" s="2">
         <v>0</v>
       </c>
       <c r="N32" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O32" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O32" s="2" t="s">
+      <c r="P32" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q32" s="17"/>
       <c r="R32" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S32" s="2"/>
       <c r="T32" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W32" s="20">
         <v>45665.490914351853</v>
@@ -8564,16 +8564,16 @@
       <c r="Y32" s="21"/>
       <c r="Z32" s="15"/>
       <c r="AA32" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AB32" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AC32" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AD32" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AE32" s="2"/>
       <c r="AF32" s="2"/>
@@ -8592,10 +8592,10 @@
       <c r="AO32" s="25"/>
       <c r="AP32" s="9"/>
       <c r="AQ32" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AR32" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
@@ -8604,14 +8604,14 @@
       <c r="AW32" s="2"/>
       <c r="AX32" s="2"/>
       <c r="AY32" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AZ32" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="AZ32" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="BA32" s="24"/>
       <c r="BB32" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="BC32" s="7"/>
       <c r="BD32" s="6"/>
@@ -8646,45 +8646,45 @@
         <v>52</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I33" s="17">
         <v>9.86</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M33" s="2">
         <v>0</v>
       </c>
       <c r="N33" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O33" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O33" s="2" t="s">
+      <c r="P33" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q33" s="17"/>
       <c r="R33" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S33" s="2"/>
       <c r="T33" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W33" s="20">
         <v>45665.490937499999</v>
@@ -8695,16 +8695,16 @@
       <c r="Y33" s="21"/>
       <c r="Z33" s="15"/>
       <c r="AA33" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AC33" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AD33" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AE33" s="2"/>
       <c r="AF33" s="2"/>
@@ -8723,10 +8723,10 @@
       <c r="AO33" s="25"/>
       <c r="AP33" s="9"/>
       <c r="AQ33" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AR33" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
@@ -8735,14 +8735,14 @@
       <c r="AW33" s="2"/>
       <c r="AX33" s="2"/>
       <c r="AY33" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AZ33" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="AZ33" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="BA33" s="24"/>
       <c r="BB33" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="BC33" s="7"/>
       <c r="BD33" s="6"/>
@@ -8777,45 +8777,45 @@
         <v>54</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I34" s="17">
         <v>9.86</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M34" s="2">
         <v>0</v>
       </c>
       <c r="N34" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O34" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O34" s="2" t="s">
+      <c r="P34" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q34" s="17"/>
       <c r="R34" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S34" s="2"/>
       <c r="T34" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W34" s="20">
         <v>45665.490949074076</v>
@@ -8826,16 +8826,16 @@
       <c r="Y34" s="21"/>
       <c r="Z34" s="15"/>
       <c r="AA34" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AC34" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AD34" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AE34" s="2"/>
       <c r="AF34" s="2"/>
@@ -8854,10 +8854,10 @@
       <c r="AO34" s="25"/>
       <c r="AP34" s="9"/>
       <c r="AQ34" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AR34" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AS34" s="2"/>
       <c r="AT34" s="2"/>
@@ -8866,14 +8866,14 @@
       <c r="AW34" s="2"/>
       <c r="AX34" s="2"/>
       <c r="AY34" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AZ34" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="AZ34" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="BA34" s="24"/>
       <c r="BB34" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="BC34" s="7"/>
       <c r="BD34" s="6"/>
@@ -8908,45 +8908,45 @@
         <v>45</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I35" s="17">
         <v>73.08</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M35" s="2">
         <v>2</v>
       </c>
       <c r="N35" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="O35" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="O35" s="2" t="s">
+      <c r="P35" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="Q35" s="17"/>
       <c r="R35" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="S35" s="2"/>
       <c r="T35" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="W35" s="20">
         <v>46120.28502314815</v>
@@ -8957,7 +8957,7 @@
       <c r="Y35" s="21"/>
       <c r="Z35" s="15"/>
       <c r="AA35" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AB35" s="2"/>
       <c r="AC35" s="2"/>
@@ -8979,10 +8979,10 @@
       <c r="AO35" s="24"/>
       <c r="AP35" s="2"/>
       <c r="AQ35" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AR35" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AS35" s="2"/>
       <c r="AT35" s="2"/>
@@ -8992,11 +8992,11 @@
       <c r="AX35" s="2"/>
       <c r="AY35" s="6"/>
       <c r="AZ35" s="8" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="BA35" s="24"/>
       <c r="BB35" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="BC35" s="2"/>
       <c r="BD35" s="2"/>
@@ -9011,485 +9011,50 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G35">
-    <cfRule type="expression" dxfId="24" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="1" stopIfTrue="1">
       <formula>G2&gt;60</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="2" stopIfTrue="1">
       <formula>G2&gt;57</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM2:AM35">
-    <cfRule type="expression" dxfId="14" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>AND(AM2&lt;TODAY()-180,AM2&gt;1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="4" stopIfTrue="1">
       <formula>AND(W2&lt;TODAY()-180,AM2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="167">
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AN28" xr:uid="{432B6907-B03F-4D6E-8F5F-82FEECD81838}">
+  <dataValidations count="22">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AN28:AN34" xr:uid="{432B6907-B03F-4D6E-8F5F-82FEECD81838}">
       <formula1>"Verde oscuro,Turquesa,Agua,Índigo,Lavanda,Rosa chicle,Bordó,Nude,Blanco,Azul marino,Crema,Rosa pálido,Suela,Naranja claro,Azul,Rosa claro,Coral claro,Coral,Celeste,Azul acero,Caqui,Beige,Rojo,Terracota,Gris,Violeta,Marrón claro,Negro,Marrón oscuro,Rosa"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AN29" xr:uid="{D1828DDD-CF77-4DB4-B7FD-CDEA003A72C6}">
-      <formula1>"Verde oscuro,Turquesa,Agua,Índigo,Lavanda,Rosa chicle,Bordó,Nude,Blanco,Azul marino,Crema,Rosa pálido,Suela,Naranja claro,Azul,Rosa claro,Coral claro,Coral,Celeste,Azul acero,Caqui,Beige,Rojo,Terracota,Gris,Violeta,Marrón claro,Negro,Marrón oscuro,Rosa"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AN30" xr:uid="{C977EF5E-A29B-4E1B-AEC5-0FF615A14BE0}">
-      <formula1>"Verde oscuro,Turquesa,Agua,Índigo,Lavanda,Rosa chicle,Bordó,Nude,Blanco,Azul marino,Crema,Rosa pálido,Suela,Naranja claro,Azul,Rosa claro,Coral claro,Coral,Celeste,Azul acero,Caqui,Beige,Rojo,Terracota,Gris,Violeta,Marrón claro,Negro,Marrón oscuro,Rosa"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AN31" xr:uid="{C05EDC65-26E1-480A-B2B3-374A3E82CCD7}">
-      <formula1>"Verde oscuro,Turquesa,Agua,Índigo,Lavanda,Rosa chicle,Bordó,Nude,Blanco,Azul marino,Crema,Rosa pálido,Suela,Naranja claro,Azul,Rosa claro,Coral claro,Coral,Celeste,Azul acero,Caqui,Beige,Rojo,Terracota,Gris,Violeta,Marrón claro,Negro,Marrón oscuro,Rosa"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AN32" xr:uid="{131E8CFA-598E-4383-9142-C0904E844255}">
-      <formula1>"Verde oscuro,Turquesa,Agua,Índigo,Lavanda,Rosa chicle,Bordó,Nude,Blanco,Azul marino,Crema,Rosa pálido,Suela,Naranja claro,Azul,Rosa claro,Coral claro,Coral,Celeste,Azul acero,Caqui,Beige,Rojo,Terracota,Gris,Violeta,Marrón claro,Negro,Marrón oscuro,Rosa"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AN33" xr:uid="{210D038B-124B-4974-B0BD-239755AA1E50}">
-      <formula1>"Verde oscuro,Turquesa,Agua,Índigo,Lavanda,Rosa chicle,Bordó,Nude,Blanco,Azul marino,Crema,Rosa pálido,Suela,Naranja claro,Azul,Rosa claro,Coral claro,Coral,Celeste,Azul acero,Caqui,Beige,Rojo,Terracota,Gris,Violeta,Marrón claro,Negro,Marrón oscuro,Rosa"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AN34" xr:uid="{790A3D09-0710-4D2D-B522-E1AB1991D710}">
-      <formula1>"Verde oscuro,Turquesa,Agua,Índigo,Lavanda,Rosa chicle,Bordó,Nude,Blanco,Azul marino,Crema,Rosa pálido,Suela,Naranja claro,Azul,Rosa claro,Coral claro,Coral,Celeste,Azul acero,Caqui,Beige,Rojo,Terracota,Gris,Violeta,Marrón claro,Negro,Marrón oscuro,Rosa"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT2" xr:uid="{C1BE4AB2-8FFE-4E96-A990-CAD1649723DA}">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT2:AT27" xr:uid="{C1BE4AB2-8FFE-4E96-A990-CAD1649723DA}">
       <formula1>"Unidad,Pack"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT3" xr:uid="{8C495162-BCB0-4235-BC9B-2703A588093B}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT4" xr:uid="{648B9FD4-932F-4983-B41E-D98F9DE4374A}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT5" xr:uid="{79652524-D157-44F4-8066-A991A87DB70F}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT6" xr:uid="{5FCA7098-29DF-4587-AA92-97A33AD996EF}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT7" xr:uid="{49F22212-1D35-49EF-A81C-C24BB7142679}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT8" xr:uid="{590F3278-42C7-4A00-9CBD-10EE89E9EE38}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT9" xr:uid="{17E2EBF9-686E-4A0A-A26D-CD430091FA73}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT10" xr:uid="{D88E39EA-0CCB-440D-A8B4-28B244DA7295}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT11" xr:uid="{45720AEE-1D2F-4D7F-B28D-29543C0AA3B9}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT12" xr:uid="{7B36F614-AE2F-4483-8478-D578CF24F109}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT13" xr:uid="{67232F44-A114-4096-A92E-6DD54F10E5E1}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT14" xr:uid="{212BA43F-6069-49B0-89CB-46889CC99A37}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT15" xr:uid="{7D50C5E8-EC32-4371-828E-67427B34EA92}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT16" xr:uid="{97EF6705-B9D5-4777-A83D-9D1193A7002E}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT17" xr:uid="{E2CD675F-BD99-4B00-9461-FBC97CF32A1C}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT18" xr:uid="{05F02776-587B-46FB-8D03-6427BAF14377}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT19" xr:uid="{ACE1FD18-7865-45BE-A0EE-E95C558819ED}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT20" xr:uid="{88B364C1-74DF-4275-A755-77DC0AFB1DDB}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT21" xr:uid="{220692C5-553A-4890-9FA0-A4CA85532E67}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT22" xr:uid="{DC45BF86-04F1-452C-9FBE-9923833A157F}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT23" xr:uid="{A65F7AC9-9444-4BA4-8CFD-84D6ED6151D4}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT24" xr:uid="{016D60E7-0DC1-4D1D-93D4-F3AEE869A2B2}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT25" xr:uid="{A775745B-E054-4685-819C-920F279BFD79}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT26" xr:uid="{390C60C1-3D4E-490B-9FD3-54F477629822}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AT27" xr:uid="{0FC86E42-C6B8-4F21-92CA-C7260BB7A7F6}">
-      <formula1>"Unidad,Pack"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX2" xr:uid="{E1135E0D-F5F7-4E02-AA0E-216A6AD847D6}">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX2:AX27" xr:uid="{E1135E0D-F5F7-4E02-AA0E-216A6AD847D6}">
       <formula1>"Baúl,Capot,Luneta"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX3" xr:uid="{D8801C6D-E2E1-4D40-8BE1-4E060443CF95}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX4" xr:uid="{81E4D17A-72A2-408E-9FE0-30E2AEA01C24}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX5" xr:uid="{8861ADC9-5D68-4479-9228-51AAC9523CE3}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX6" xr:uid="{301AE5DC-A3FD-49D1-9931-4187E58ACD40}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX7" xr:uid="{57C5536E-1683-4FA5-84C9-403512D90B88}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX8" xr:uid="{017D589A-377A-47E8-9055-B5240A8C8577}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX9" xr:uid="{802E6D6D-E335-4E1B-A27A-DC4E43787C5E}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX10" xr:uid="{3FF89208-160D-4DE4-A109-D313145E2C00}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX11" xr:uid="{2ABF4301-F898-4893-99F9-1C3A56125B03}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX12" xr:uid="{5A8C2308-DC97-479D-932B-9054872A2035}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX13" xr:uid="{4D3725CE-F27E-4566-A26C-8887C8E58FC8}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX14" xr:uid="{4AEDE693-6F7E-48F9-B6A5-AD0B99E2F76B}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX15" xr:uid="{41283B27-499D-4220-A9AC-97ED60B279BC}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX16" xr:uid="{79906346-0D3D-427D-AEDC-292E5C4B5F07}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX17" xr:uid="{E97FA964-4AD7-4857-A6F1-5A153FF83950}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX18" xr:uid="{5FFFCECF-38C2-4676-90BA-D62AC0D37A96}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX19" xr:uid="{E206E09C-C024-433D-BCEE-5FE2EA6C4463}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX20" xr:uid="{8A1161E5-8702-4D10-9E58-50522B5D34F4}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX21" xr:uid="{484B5297-43B8-483C-8BB1-B691F6979794}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX22" xr:uid="{7CF524E0-613F-452A-9E2D-D9D5A80B8B97}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX23" xr:uid="{3376ECF2-BF52-494B-B4FC-2BB4D5623A63}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX24" xr:uid="{A30D1236-E38D-418B-B011-2E58C1161100}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX25" xr:uid="{F254F905-77A2-4496-97B1-079D1F341100}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX26" xr:uid="{43B1337E-4C24-4FDF-8AA5-DC45C25FBDBB}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AX27" xr:uid="{40D218F7-42BB-43A7-A815-E3C2CF951F39}">
-      <formula1>"Baúl,Capot,Luneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AY28" xr:uid="{12FB3A00-4AA5-41DD-ACB1-34A7CF5CA72C}">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AY28:AY35" xr:uid="{12FB3A00-4AA5-41DD-ACB1-34A7CF5CA72C}">
       <formula1>"Alemania,Argentina,Brasil,China,Estados Unidos,Francia,Japón,México"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AY29" xr:uid="{393A1C0A-929A-4FD9-9176-4C5D3B475DE7}">
-      <formula1>"Alemania,Argentina,Brasil,China,Estados Unidos,Francia,Japón,México"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AY30" xr:uid="{9086D658-2A98-48E0-B2C1-2C5313834573}">
-      <formula1>"Alemania,Argentina,Brasil,China,Estados Unidos,Francia,Japón,México"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AY31" xr:uid="{59F69199-5094-4021-9378-26705C2BF2FB}">
-      <formula1>"Alemania,Argentina,Brasil,China,Estados Unidos,Francia,Japón,México"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AY32" xr:uid="{AA0197F6-2B91-41D4-A5B9-47819A313DF9}">
-      <formula1>"Alemania,Argentina,Brasil,China,Estados Unidos,Francia,Japón,México"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AY33" xr:uid="{27CA0887-998C-4595-A617-D6325342DFD8}">
-      <formula1>"Alemania,Argentina,Brasil,China,Estados Unidos,Francia,Japón,México"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AY34" xr:uid="{A8F2568A-9BB0-4BE3-8173-BC4540FFB93B}">
-      <formula1>"Alemania,Argentina,Brasil,China,Estados Unidos,Francia,Japón,México"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AY35" xr:uid="{3F1FAE80-0FF9-4995-A9FA-DAF842724BCA}">
-      <formula1>"Alemania,Argentina,Brasil,China,Estados Unidos,Francia,Japón,México"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ2" xr:uid="{CA3B71E8-7ECC-4A24-B1AC-EAF1CBDCD03D}">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ35 AZ2:AZ27" xr:uid="{CA3B71E8-7ECC-4A24-B1AC-EAF1CBDCD03D}">
       <formula1>"Carro/Camioneta"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ3" xr:uid="{6B6C9B25-C431-4581-9EC2-9416C2D2A3F2}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ4" xr:uid="{A97220AE-B389-4CC6-BBD7-2B59C917D10E}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ5" xr:uid="{2DFFFEDF-53A6-4BC3-995A-457D278DAAD5}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ6" xr:uid="{E3BCE327-FA0A-44BC-8ED4-43E2C643F9DC}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ7" xr:uid="{89C6BA31-D61A-4EEE-97BD-1A048FE9ECFE}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ8" xr:uid="{532DB6B2-640C-42D8-8EB4-A6DC684A1A3C}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ9" xr:uid="{CD6516AC-120C-4C0D-BF4E-66DFC9F7A572}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ10" xr:uid="{4324EB9E-D15E-4E05-8C07-78920F9F2872}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ11" xr:uid="{AD178B8D-8B96-4EF5-8BC0-0BC7CFDD382B}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ12" xr:uid="{C217C03E-FCBD-4621-BCA2-FB4C06C739EF}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ13" xr:uid="{57C11A37-3311-4ECB-8C98-8EFE9B548D34}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ14" xr:uid="{053B9793-2372-4A71-BA49-0A1F63B2C615}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ15" xr:uid="{7A43853E-C98A-4365-BC33-A113ECC62B0D}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ16" xr:uid="{941466E4-A0E9-4FF6-83D1-FED5B037AECD}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ17" xr:uid="{F33E139B-CA09-4D3D-B8F6-EA937F424175}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ18" xr:uid="{2762150B-4EA1-440E-8B9A-4C00E4145F5A}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ19" xr:uid="{710538C3-4DB3-4E1A-A849-52D9ECCBA0DD}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ20" xr:uid="{513CE97B-3465-4B13-BDEE-AECA7D3B6578}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ21" xr:uid="{3624A499-B4D2-4D4D-AB63-EB44A8CF3F10}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ22" xr:uid="{113A23BF-8198-4E89-9B07-1F823FB87C0D}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ23" xr:uid="{C26EB53D-0249-43D1-8C92-F6B13D89BA9C}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ24" xr:uid="{94999828-2F37-40A4-BF7A-AED96C2218AD}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ25" xr:uid="{73D468E3-5262-4D75-90FF-E6F1F44C0CC0}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ26" xr:uid="{343975BB-BAF5-440F-A33C-E72481C06CEC}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ27" xr:uid="{A593E069-8424-4AEA-932F-C965F484AD8E}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ28" xr:uid="{BB41CBA2-4BB0-477B-8863-AB9231DF41D1}">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ28:AZ34" xr:uid="{BB41CBA2-4BB0-477B-8863-AB9231DF41D1}">
       <formula1>"Carro/Camioneta,Moto/Cuatriciclo,Línea Pesada,Agrícola"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ29" xr:uid="{337F40FC-FE0F-4BF9-B9C6-547600C9C6EE}">
-      <formula1>"Carro/Camioneta,Moto/Cuatriciclo,Línea Pesada,Agrícola"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ30" xr:uid="{8D0E1748-89FF-46C0-8D1B-9CC58D35F9F4}">
-      <formula1>"Carro/Camioneta,Moto/Cuatriciclo,Línea Pesada,Agrícola"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ31" xr:uid="{C86C7A24-01C2-4C4C-87F0-BF90F38ED250}">
-      <formula1>"Carro/Camioneta,Moto/Cuatriciclo,Línea Pesada,Agrícola"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ32" xr:uid="{8EF28FE9-C865-46DB-81C9-1C13C7686F99}">
-      <formula1>"Carro/Camioneta,Moto/Cuatriciclo,Línea Pesada,Agrícola"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ33" xr:uid="{50116F88-EB52-4B03-9A0B-7F584978DB39}">
-      <formula1>"Carro/Camioneta,Moto/Cuatriciclo,Línea Pesada,Agrícola"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ34" xr:uid="{0FB2BA5C-F633-4B12-A3E0-FAA6C161D3DC}">
-      <formula1>"Carro/Camioneta,Moto/Cuatriciclo,Línea Pesada,Agrícola"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="AZ35" xr:uid="{468FC81A-5C31-4227-B9BB-7D797D4FA565}">
-      <formula1>"Carro/Camioneta"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC2" xr:uid="{0C9B15B8-DE57-429A-9496-C1E40FCEDD4B}">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC2:BC34" xr:uid="{0C9B15B8-DE57-429A-9496-C1E40FCEDD4B}">
       <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC3" xr:uid="{B76918E2-6B5F-42A2-9785-6AFF8F7C1354}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC4" xr:uid="{6D6A5295-E02E-4356-88DA-9188B5F4F95F}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC5" xr:uid="{190ECF90-E81E-45EC-991C-E0C1D767A566}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC6" xr:uid="{5419881B-15DC-4525-B01E-5883F32DA59A}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC7" xr:uid="{F035027F-892B-4EE5-AE2F-2D16BB1E876D}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC8" xr:uid="{098E2354-F423-4324-AE03-AE8676A24FA0}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC9" xr:uid="{3064E505-09D4-4080-8FD2-B9743AA720BC}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC10" xr:uid="{70696248-7EC6-4669-81CD-64A464ECFD7A}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC11" xr:uid="{AF163C85-FECB-454B-B216-8AFE1C4D7E42}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC12" xr:uid="{C5AB8DC8-4D76-4949-8870-F9892EECE475}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC13" xr:uid="{9685EF2C-D7FE-4BF2-9E36-76C29FBBAC12}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC14" xr:uid="{A00D188E-D1A4-41CE-A4C7-EFB9757A1F75}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC15" xr:uid="{1C906C5F-9EA2-4E40-A91A-D919638B67F7}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC16" xr:uid="{D70DB259-82D4-45A9-8A73-D8ABC730A7DF}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC17" xr:uid="{C29FA1F2-49D0-4FB5-9D2E-CCFDE802F0C9}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC18" xr:uid="{827E0DDC-02B3-4343-A94E-E6424D77EA35}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC19" xr:uid="{657344B3-BB4B-4D27-A2D2-7AD36DB245A6}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC20" xr:uid="{9460D962-934C-4C5C-A07D-1E8E733A2BAB}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC21" xr:uid="{58631472-23D0-4CFB-820E-22ADC619B5B2}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC22" xr:uid="{623F907C-8E27-4B30-83C2-0DC282E81FE7}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC23" xr:uid="{81FEDDDA-E40F-4ECE-86B5-8029EFD800CE}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC24" xr:uid="{8144C599-93F9-417C-8AB6-7286B434B2E4}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC25" xr:uid="{045C6524-454B-4309-8BAF-AF4830F8AE3B}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC26" xr:uid="{AA65DE33-0FC4-40D8-BAD9-1181482FFDE3}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC27" xr:uid="{754F8DC5-CF48-427A-AB96-1DA4C76826E7}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC28" xr:uid="{CB6EC4D9-B89F-4310-808B-9822A5A503F7}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC29" xr:uid="{36FB89F6-7EF2-41BF-9163-FCE28290907B}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC30" xr:uid="{F863A6EC-40A4-495A-8D6F-598C5F7291DB}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC31" xr:uid="{5A51238B-847A-4EE5-969D-26551618AA79}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC32" xr:uid="{A10A19FD-BF60-4DDE-8BDC-83DFE4AC83C2}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC33" xr:uid="{B7A350D9-2182-4376-B61C-F0C76797F0BB}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BC34" xr:uid="{39A709C4-B893-4321-85FD-D3969B7B8127}">
-      <formula1>"El producto es una pieza artesanal,El producto es un kit o un pack,El producto no tiene código registrado,Otra razón"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BD28" xr:uid="{F844E4A0-7962-4D68-9528-01A4CD74BD65}">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BD28:BD34" xr:uid="{F844E4A0-7962-4D68-9528-01A4CD74BD65}">
       <formula1>"Carbón,Cobre"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BD29" xr:uid="{26830CA6-FDAF-4DF7-90C1-0AE9F3EC4F0C}">
-      <formula1>"Carbón,Cobre"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BD30" xr:uid="{C226D46D-C72A-4A64-AD13-2DF8352730E2}">
-      <formula1>"Carbón,Cobre"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BD31" xr:uid="{080C590B-84AB-40E0-ACE8-0E0A1F3FEB77}">
-      <formula1>"Carbón,Cobre"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BD32" xr:uid="{4819B27F-E986-400F-991D-8779772CE1C4}">
-      <formula1>"Carbón,Cobre"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BD33" xr:uid="{3403229F-F724-4AB2-AFB4-09C9B3F1048B}">
-      <formula1>"Carbón,Cobre"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BD34" xr:uid="{6CBC2418-62C2-4FC9-B280-D0A91BC5A528}">
-      <formula1>"Carbón,Cobre"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BG28" xr:uid="{2138E39F-207B-4D82-BD89-F74225E5DD66}">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BG28:BG34" xr:uid="{2138E39F-207B-4D82-BD89-F74225E5DD66}">
       <formula1>"No,Sí"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BG29" xr:uid="{C8E13923-840C-49DE-A946-C150B508A75A}">
-      <formula1>"No,Sí"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BG30" xr:uid="{2D71AD88-940D-4858-A542-5A35432CE6F2}">
-      <formula1>"No,Sí"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BG31" xr:uid="{0555B71A-8F54-418D-98E4-789A8E24CA3F}">
-      <formula1>"No,Sí"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BG32" xr:uid="{062B0DAD-41B6-46F6-9580-2EB235029CA1}">
-      <formula1>"No,Sí"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BG33" xr:uid="{862D4D0E-6A47-443E-9E54-FA2E291FDB37}">
-      <formula1>"No,Sí"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BG34" xr:uid="{BC825C66-7D05-46DC-8D55-6E9E97836B18}">
-      <formula1>"No,Sí"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BI28" xr:uid="{B86F5289-14D6-42CB-BABB-DF86B36ABBD8}">
-      <formula1>"Acero inoxidable,Aluminio"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BI29" xr:uid="{DF2C7271-9724-4EB8-B46A-5369FF6807A7}">
-      <formula1>"Acero inoxidable,Aluminio"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BI30" xr:uid="{8FED14E3-A0A6-4E1C-8983-769E25E9A98F}">
-      <formula1>"Acero inoxidable,Aluminio"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BI31" xr:uid="{F38747E4-C3A2-44B9-A909-BB7EA34C6F83}">
-      <formula1>"Acero inoxidable,Aluminio"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BI32" xr:uid="{AA7E673F-474B-4CB5-B28D-A5FC402F32E1}">
-      <formula1>"Acero inoxidable,Aluminio"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BI33" xr:uid="{73C308AC-C332-47AA-8FA9-F60CD1BDE4E5}">
-      <formula1>"Acero inoxidable,Aluminio"</formula1>
-    </dataValidation>
-    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BI34" xr:uid="{C3D81EC4-86A4-4CB7-A074-9E2E42960574}">
+    <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BI28:BI34" xr:uid="{B86F5289-14D6-42CB-BABB-DF86B36ABBD8}">
       <formula1>"Acero inoxidable,Aluminio"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" operator="equal" allowBlank="1" showInputMessage="1" sqref="BI35" xr:uid="{DF8C1E27-CE49-40E9-AFBD-65F9AF571191}">
